--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2440C56-AA99-4B8F-AF31-BABBDA11B8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3800D363-DE19-4312-994D-9BFCC0F5B12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="47">
   <si>
     <t>日付</t>
   </si>
@@ -1208,392 +1208,182 @@
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A37" s="6">
-        <v>45901</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37">
-        <v>893702</v>
-      </c>
+      <c r="A37" s="6"/>
+      <c r="B37" s="5"/>
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A38" s="6">
-        <v>45902</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38">
-        <v>605002</v>
-      </c>
+      <c r="A38" s="6"/>
+      <c r="B38" s="5"/>
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A39" s="6">
-        <v>45903</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39">
-        <v>390202</v>
-      </c>
+      <c r="A39" s="6"/>
+      <c r="B39" s="5"/>
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A40" s="6">
-        <v>45904</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40">
-        <v>295118</v>
-      </c>
+      <c r="A40" s="6"/>
+      <c r="B40" s="5"/>
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A41" s="6">
-        <v>45905</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41">
-        <v>2477938</v>
-      </c>
+      <c r="A41" s="6"/>
+      <c r="B41" s="5"/>
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A42" s="6">
-        <v>45906</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42">
-        <v>419740</v>
-      </c>
+      <c r="A42" s="6"/>
+      <c r="B42" s="5"/>
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A43" s="6">
-        <v>45907</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43">
-        <v>3694896</v>
-      </c>
+      <c r="A43" s="6"/>
+      <c r="B43" s="5"/>
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A44" s="6">
-        <v>45908</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C44">
-        <v>257834</v>
-      </c>
+      <c r="A44" s="6"/>
+      <c r="B44" s="5"/>
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A45" s="6">
-        <v>45909</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45">
-        <v>420241</v>
-      </c>
+      <c r="A45" s="6"/>
+      <c r="B45" s="5"/>
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A46" s="6">
-        <v>45910</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C46">
-        <v>1628126</v>
-      </c>
+      <c r="A46" s="6"/>
+      <c r="B46" s="5"/>
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="6">
-        <v>45911</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C47">
-        <v>2060739</v>
-      </c>
+      <c r="A47" s="6"/>
+      <c r="B47" s="5"/>
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="6">
-        <v>45912</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C48">
-        <v>439136</v>
-      </c>
+      <c r="A48" s="6"/>
+      <c r="B48" s="5"/>
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A49" s="6">
-        <v>45913</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C49">
-        <v>350071</v>
-      </c>
+      <c r="A49" s="6"/>
+      <c r="B49" s="5"/>
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A50" s="6">
-        <v>45914</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C50">
-        <v>3141159</v>
-      </c>
+      <c r="A50" s="6"/>
+      <c r="B50" s="5"/>
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A51" s="6">
-        <v>45915</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51">
-        <v>2504715</v>
-      </c>
+      <c r="A51" s="6"/>
+      <c r="B51" s="5"/>
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A52" s="6">
-        <v>45916</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C52">
-        <v>348090</v>
-      </c>
+      <c r="A52" s="6"/>
+      <c r="B52" s="5"/>
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A53" s="6">
-        <v>45917</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C53">
-        <v>391273</v>
-      </c>
+      <c r="A53" s="6"/>
+      <c r="B53" s="5"/>
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A54" s="6">
-        <v>45918</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C54">
-        <v>309063</v>
-      </c>
+      <c r="A54" s="6"/>
+      <c r="B54" s="5"/>
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A55" s="6">
-        <v>45919</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C55">
-        <v>174092</v>
-      </c>
+      <c r="A55" s="6"/>
+      <c r="B55" s="5"/>
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A56" s="6">
-        <v>45920</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C56">
-        <v>5507581</v>
-      </c>
+      <c r="A56" s="6"/>
+      <c r="B56" s="5"/>
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A57" s="6">
-        <v>45921</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C57">
-        <v>7935803</v>
-      </c>
+      <c r="A57" s="6"/>
+      <c r="B57" s="5"/>
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A58" s="6">
-        <v>45922</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C58">
-        <v>667960</v>
-      </c>
+      <c r="A58" s="6"/>
+      <c r="B58" s="5"/>
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A59" s="6">
-        <v>45923</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C59">
-        <v>326209</v>
-      </c>
+      <c r="A59" s="6"/>
+      <c r="B59" s="5"/>
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A60" s="6">
-        <v>45924</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C60">
-        <v>254433</v>
-      </c>
+      <c r="A60" s="6"/>
+      <c r="B60" s="5"/>
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A61" s="6">
-        <v>45925</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C61">
-        <v>1445378</v>
-      </c>
+      <c r="A61" s="6"/>
+      <c r="B61" s="5"/>
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A62" s="6">
-        <v>45926</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C62">
-        <v>339822</v>
-      </c>
+      <c r="A62" s="6"/>
+      <c r="B62" s="5"/>
       <c r="D62" s="7"/>
       <c r="E62" s="5"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A63" s="6">
-        <v>45927</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C63">
-        <v>311479</v>
-      </c>
+      <c r="A63" s="6"/>
+      <c r="B63" s="5"/>
       <c r="D63" s="7"/>
       <c r="E63" s="5"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A64" s="6">
-        <v>45928</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C64">
-        <v>4667587</v>
-      </c>
+      <c r="A64" s="6"/>
+      <c r="B64" s="5"/>
       <c r="D64" s="7"/>
       <c r="E64" s="5"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A65" s="6">
-        <v>45929</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C65">
-        <v>304397</v>
-      </c>
+      <c r="A65" s="6"/>
+      <c r="B65" s="5"/>
       <c r="D65" s="7"/>
       <c r="E65" s="5"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A66" s="6">
-        <v>45930</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C66">
-        <v>544908</v>
-      </c>
+      <c r="A66" s="6"/>
+      <c r="B66" s="5"/>
       <c r="D66" s="7"/>
       <c r="E66" s="5"/>
     </row>

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1721</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -205,29 +205,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,8 +226,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,9 +241,62 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,15 +310,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -302,46 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +410,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +434,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,31 +458,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,61 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,31 +500,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,6 +531,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,22 +635,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -649,22 +664,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,149 +683,149 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1722"/>
+  <dimension ref="A1:E1723"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -22980,8 +22980,19 @@
         <v>475404</v>
       </c>
     </row>
+    <row r="1723" spans="1:3">
+      <c r="A1723" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1723">
+        <v>402682</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1721">
+  <autoFilter ref="A1:E1722">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,32 +203,16 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,7 +226,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,37 +256,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -303,10 +263,18 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -333,8 +301,40 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,25 +392,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +422,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +458,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +488,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,13 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,73 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -582,6 +597,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,6 +627,33 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -615,217 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1723"/>
+  <dimension ref="A1:E1724"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -22991,8 +22991,19 @@
         <v>402682</v>
       </c>
     </row>
+    <row r="1724" spans="1:3">
+      <c r="A1724" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1724">
+        <v>390267</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1722">
+  <autoFilter ref="A1:E1723">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,28 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -239,9 +217,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,15 +233,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,8 +247,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -290,13 +282,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -316,6 +301,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -325,10 +325,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +380,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +398,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,127 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,6 +587,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -603,26 +618,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -638,9 +636,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -649,7 +649,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1724"/>
+  <dimension ref="A1:E1725"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23002,8 +23002,19 @@
         <v>390267</v>
       </c>
     </row>
+    <row r="1725" spans="1:3">
+      <c r="A1725" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1725">
+        <v>17006577</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1723">
+  <autoFilter ref="A1:E1724">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -217,8 +217,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,8 +240,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -247,31 +264,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,23 +288,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,7 +310,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,7 +324,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -333,17 +332,18 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,19 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +380,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,6 +458,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -434,7 +488,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,25 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,67 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,31 +571,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -620,16 +605,37 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -649,22 +655,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1725"/>
+  <dimension ref="A1:E1726"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23013,8 +23013,19 @@
         <v>17006577</v>
       </c>
     </row>
+    <row r="1726" spans="1:3">
+      <c r="A1726" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1726">
+        <v>657555</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1724">
+  <autoFilter ref="A1:E1725">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
@@ -217,16 +217,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,7 +256,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -258,7 +273,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,32 +308,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -317,22 +325,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -340,10 +333,17 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,31 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,25 +386,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,13 +410,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,85 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -605,7 +599,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -655,16 +649,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1726"/>
+  <dimension ref="A1:E1727"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23024,8 +23024,19 @@
         <v>657555</v>
       </c>
     </row>
+    <row r="1727" spans="1:3">
+      <c r="A1727" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1727">
+        <v>5505999</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1725">
+  <autoFilter ref="A1:E1726">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,6 +204,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -211,7 +226,68 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,7 +301,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -240,32 +316,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -281,67 +342,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,43 +488,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,49 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,73 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,6 +610,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -615,41 +639,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +657,175 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1727"/>
+  <dimension ref="A1:E1728"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23035,8 +23035,19 @@
         <v>5505999</v>
       </c>
     </row>
+    <row r="1728" spans="1:3">
+      <c r="A1728" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1728">
+        <v>1027925</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1726">
+  <autoFilter ref="A1:E1727">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,15 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,7 +225,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,6 +233,22 @@
     <font>
       <b/>
       <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -257,7 +272,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -272,7 +287,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,28 +295,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -310,7 +311,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,9 +333,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,30 +362,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -398,19 +374,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +428,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +458,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,19 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,43 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,6 +591,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,33 +619,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -639,6 +630,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,11 +662,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1728"/>
+  <dimension ref="A1:E1729"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23046,8 +23046,19 @@
         <v>1027925</v>
       </c>
     </row>
+    <row r="1729" spans="1:3">
+      <c r="A1729" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1729">
+        <v>442847</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1727">
+  <autoFilter ref="A1:E1728">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,6 +204,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -217,15 +232,70 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -239,25 +309,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,62 +332,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,25 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,13 +386,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +398,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +428,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +458,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,19 +506,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,73 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -597,9 +588,29 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,32 +626,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,25 +653,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,124 +695,124 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1729"/>
+  <dimension ref="A1:E1730"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23057,8 +23057,19 @@
         <v>442847</v>
       </c>
     </row>
+    <row r="1730" spans="1:3">
+      <c r="A1730" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1730">
+        <v>2530240</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1728">
+  <autoFilter ref="A1:E1729">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1730</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -211,114 +211,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,16 +234,116 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,19 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +374,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,24 +398,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -440,13 +410,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,79 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,6 +586,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -593,24 +608,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -626,21 +623,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,151 +650,169 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1730"/>
+  <dimension ref="A1:E1731"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23068,8 +23068,19 @@
         <v>2530240</v>
       </c>
     </row>
+    <row r="1731" spans="1:3">
+      <c r="A1731" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1731">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1729">
+  <autoFilter ref="A1:E1730">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1731</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,7 +234,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,8 +247,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -247,34 +263,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -294,14 +287,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -311,22 +296,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,9 +309,39 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +374,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +428,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,97 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,25 +500,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,6 +537,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -586,11 +601,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,17 +631,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -644,188 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1732"/>
+  <dimension ref="A1:E1733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23090,8 +23090,19 @@
         <v>14993362</v>
       </c>
     </row>
+    <row r="1733" spans="1:3">
+      <c r="A1733" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1733">
+        <v>504903</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1731">
+  <autoFilter ref="A1:E1732">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,6 +204,51 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -219,29 +264,44 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,14 +323,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -280,59 +332,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,7 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,31 +416,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,13 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +446,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +470,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +494,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,73 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,45 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -586,17 +625,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,39 +658,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -659,173 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1733"/>
+  <dimension ref="A1:E1734"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23101,8 +23101,19 @@
         <v>504903</v>
       </c>
     </row>
+    <row r="1734" spans="1:3">
+      <c r="A1734" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1734">
+        <v>590567</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1732">
+  <autoFilter ref="A1:E1733">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1734</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -210,18 +210,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -232,24 +240,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,24 +256,25 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -300,32 +293,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,9 +325,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,49 +398,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,25 +428,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +488,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,49 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -586,11 +595,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,35 +625,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,6 +651,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1734"/>
+  <dimension ref="A1:E1735"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23112,8 +23112,16 @@
         <v>590567</v>
       </c>
     </row>
+    <row r="1735" spans="1:2">
+      <c r="A1735" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1733">
+  <autoFilter ref="A1:E1734">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1735</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,6 +203,59 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -211,7 +264,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,67 +302,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,10 +325,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -325,23 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +410,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,31 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,31 +452,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,18 +482,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -494,31 +494,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,29 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,20 +613,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,11 +643,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,166 +668,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1736"/>
+  <dimension ref="A1:E1737"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23134,8 +23134,19 @@
         <v>726855</v>
       </c>
     </row>
+    <row r="1737" spans="1:3">
+      <c r="A1737" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1737">
+        <v>853683</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1735">
+  <autoFilter ref="A1:E1736">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,15 +204,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -226,24 +218,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,16 +247,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,32 +270,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,7 +279,39 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,6 +325,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -339,9 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,91 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,19 +476,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,13 +488,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +506,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,26 +574,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,21 +611,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -639,6 +621,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1737"/>
+  <dimension ref="A1:E1738"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23145,8 +23145,19 @@
         <v>853683</v>
       </c>
     </row>
+    <row r="1738" spans="1:3">
+      <c r="A1738" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1738">
+        <v>691414</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1736">
+  <autoFilter ref="A1:E1737">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,42 +204,14 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -247,9 +219,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,14 +236,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,33 +257,46 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -325,16 +310,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -344,6 +328,22 @@
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,37 +440,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,79 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,28 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,41 +612,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,12 +645,25 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1738"/>
+  <dimension ref="A1:E1739"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23156,8 +23156,19 @@
         <v>691414</v>
       </c>
     </row>
+    <row r="1739" spans="1:3">
+      <c r="A1739" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1739">
+        <v>11969269</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1737">
+  <autoFilter ref="A1:E1738">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,17 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,30 +218,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -266,9 +235,46 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -288,15 +294,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,39 +341,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +386,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,55 +410,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,7 +488,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,79 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,32 +572,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -615,32 +589,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,7 +614,57 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
         <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1739"/>
+  <dimension ref="A1:E1740"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23167,8 +23167,19 @@
         <v>11969269</v>
       </c>
     </row>
+    <row r="1740" spans="1:3">
+      <c r="A1740" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1740">
+        <v>1864858</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1738">
+  <autoFilter ref="A1:E1739">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,121 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,6 +220,120 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -341,7 +341,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,31 +380,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,43 +404,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +446,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,25 +506,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,19 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,39 +593,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,11 +623,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,151 +659,160 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1740"/>
+  <dimension ref="A1:E1741"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23178,8 +23178,19 @@
         <v>1864858</v>
       </c>
     </row>
+    <row r="1741" spans="1:3">
+      <c r="A1741" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1741">
+        <v>334273</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1739">
+  <autoFilter ref="A1:E1740">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -204,7 +204,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,24 +248,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,14 +272,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,31 +286,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,17 +325,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -335,13 +342,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,150 +362,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -518,7 +374,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,7 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,6 +621,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -625,22 +649,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,160 +668,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1741"/>
+  <dimension ref="A1:E1742"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23189,8 +23189,19 @@
         <v>334273</v>
       </c>
     </row>
+    <row r="1742" spans="1:3">
+      <c r="A1742" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1742">
+        <v>261022</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1740">
+  <autoFilter ref="A1:E1741">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,45 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -218,16 +257,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,6 +288,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,18 +308,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -271,24 +324,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,46 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,19 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,115 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,13 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,6 +537,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -580,13 +595,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,17 +634,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -638,33 +660,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1742"/>
+  <dimension ref="A1:E1743"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23200,8 +23200,19 @@
         <v>261022</v>
       </c>
     </row>
+    <row r="1743" spans="1:3">
+      <c r="A1743" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1743">
+        <v>495913</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1741">
+  <autoFilter ref="A1:E1742">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
@@ -205,67 +205,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -280,7 +219,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,8 +262,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,14 +272,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -332,16 +294,54 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,37 +458,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,109 +524,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,54 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -643,6 +595,50 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -658,13 +654,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1743"/>
+  <dimension ref="A1:E1744"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23211,8 +23211,19 @@
         <v>495913</v>
       </c>
     </row>
+    <row r="1744" spans="1:3">
+      <c r="A1744" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1744">
+        <v>241100</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1742">
+  <autoFilter ref="A1:E1743">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,8 +204,46 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,14 +257,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -248,44 +286,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -294,24 +294,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,16 +325,23 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,127 +464,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,19 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +512,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,25 +572,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -600,6 +591,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,6 +621,30 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -638,55 +668,25 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,137 +695,137 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1744"/>
+  <dimension ref="A1:E1745"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23222,8 +23222,19 @@
         <v>241100</v>
       </c>
     </row>
+    <row r="1745" spans="1:3">
+      <c r="A1745" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1745">
+        <v>288120</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1743">
+  <autoFilter ref="A1:E1744">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,18 +203,33 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -226,16 +241,15 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,6 +263,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -264,23 +279,23 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,23 +303,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,16 +323,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,43 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,43 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -477,72 +543,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -590,22 +610,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -635,36 +655,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1745"/>
+  <dimension ref="A1:E1746"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23233,8 +23233,19 @@
         <v>288120</v>
       </c>
     </row>
+    <row r="1746" spans="1:3">
+      <c r="A1746" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1746">
+        <v>9744899</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1744">
+  <autoFilter ref="A1:E1745">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,9 +166,9 @@
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -211,7 +211,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,7 +249,45 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,25 +301,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -271,6 +325,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -278,70 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,151 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,22 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,16 +611,34 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -647,24 +660,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1746"/>
+  <dimension ref="A1:E1747"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23244,8 +23244,19 @@
         <v>9744899</v>
       </c>
     </row>
+    <row r="1747" spans="1:3">
+      <c r="A1747" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1747">
+        <v>384003</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1745">
+  <autoFilter ref="A1:E1746">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,51 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,8 +261,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,16 +284,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,68 +326,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -328,13 +335,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,37 +434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,49 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,13 +470,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -582,6 +597,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,48 +630,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,6 +651,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1747"/>
+  <dimension ref="A1:E1748"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23255,8 +23255,19 @@
         <v>384003</v>
       </c>
     </row>
+    <row r="1748" spans="1:3">
+      <c r="A1748" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1748">
+        <v>384003</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1746">
+  <autoFilter ref="A1:E1747">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,7 +204,50 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,56 +269,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -284,16 +277,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -309,10 +301,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -325,8 +317,16 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,7 +334,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,37 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,43 +506,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,85 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,20 +606,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,6 +632,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -657,162 +668,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1748"/>
+  <dimension ref="A1:E1749"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23266,8 +23266,19 @@
         <v>384003</v>
       </c>
     </row>
+    <row r="1749" spans="1:3">
+      <c r="A1749" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1749">
+        <v>212216</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1747">
+  <autoFilter ref="A1:E1748">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -204,14 +204,53 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,7 +264,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,61 +287,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,14 +295,6 @@
     <font>
       <b/>
       <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -326,9 +311,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -342,6 +327,21 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,25 +380,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,13 +410,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,91 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,26 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -607,21 +587,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -632,15 +597,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,8 +619,52 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,85 +692,76 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -779,40 +770,49 @@
     <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1749"/>
+  <dimension ref="A1:E1750"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23277,8 +23277,19 @@
         <v>212216</v>
       </c>
     </row>
+    <row r="1750" spans="1:3">
+      <c r="A1750" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1750">
+        <v>544535</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1748">
+  <autoFilter ref="A1:E1749">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1750</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,28 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,14 +238,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -240,9 +277,55 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,94 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,97 +380,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +404,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,6 +591,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,26 +625,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -657,33 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1750"/>
+  <dimension ref="A1:E1751"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23288,8 +23288,19 @@
         <v>544535</v>
       </c>
     </row>
+    <row r="1751" spans="1:3">
+      <c r="A1751" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1751">
+        <v>3326633</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1749">
+  <autoFilter ref="A1:E1750">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1750</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,31 +203,11 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -238,32 +218,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -292,6 +263,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -301,13 +280,42 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -323,27 +331,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,31 +386,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,13 +422,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,19 +446,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +476,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,13 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,19 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,45 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -627,11 +588,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -662,9 +636,35 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1751"/>
+  <dimension ref="A1:E1752"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23299,8 +23299,19 @@
         <v>3326633</v>
       </c>
     </row>
+    <row r="1752" spans="1:3">
+      <c r="A1752" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1752">
+        <v>416499</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1750">
+  <autoFilter ref="A1:E1751">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -205,14 +205,36 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,83 +249,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,13 +264,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -336,6 +282,60 @@
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +392,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +494,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,139 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,65 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -596,21 +655,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -624,208 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1752"/>
+  <dimension ref="A1:E1754"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23310,8 +23310,30 @@
         <v>416499</v>
       </c>
     </row>
+    <row r="1753" spans="1:3">
+      <c r="A1753" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1753">
+        <v>416499</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:3">
+      <c r="A1754" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1754">
+        <v>286065</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1751">
+  <autoFilter ref="A1:E1753">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,6 +204,89 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -218,15 +301,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,37 +317,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -279,38 +327,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -323,25 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,25 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,19 +404,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,121 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,20 +573,39 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -608,9 +627,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,41 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1754"/>
+  <dimension ref="A1:E1755"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23332,8 +23332,19 @@
         <v>286065</v>
       </c>
     </row>
+    <row r="1755" spans="1:3">
+      <c r="A1755" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1755">
+        <v>11264425</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1753">
+  <autoFilter ref="A1:E1754">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,14 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -218,61 +210,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,9 +232,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,9 +246,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -319,14 +279,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -334,7 +286,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -344,6 +296,54 @@
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -368,7 +368,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,55 +392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,43 +404,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +422,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +512,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,8 +574,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,52 +610,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,6 +634,32 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1755"/>
+  <dimension ref="A1:E1756"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23343,8 +23343,19 @@
         <v>11264425</v>
       </c>
     </row>
+    <row r="1756" spans="1:3">
+      <c r="A1756" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1756">
+        <v>486461</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1754">
+  <autoFilter ref="A1:E1755">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,77 +203,19 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -293,15 +235,67 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -323,9 +317,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,17 +341,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,91 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,73 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,22 +629,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,173 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1756"/>
+  <dimension ref="A1:E1757"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23354,8 +23354,19 @@
         <v>486461</v>
       </c>
     </row>
+    <row r="1757" spans="1:3">
+      <c r="A1757" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1757">
+        <v>520155</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1755">
+  <autoFilter ref="A1:E1756">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,25 +203,38 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,15 +254,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,23 +286,24 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,7 +326,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,30 +341,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,37 +386,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,13 +482,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,109 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,69 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -658,6 +595,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -668,164 +629,203 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1757"/>
+  <dimension ref="A1:E1758"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23365,8 +23365,19 @@
         <v>520155</v>
       </c>
     </row>
+    <row r="1758" spans="1:3">
+      <c r="A1758" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1758">
+        <v>240484</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1756">
+  <autoFilter ref="A1:E1757">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1758</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,30 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -217,16 +241,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,29 +257,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -277,23 +293,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -301,24 +300,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,15 +333,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,13 +392,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,37 +434,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +476,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,13 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,49 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,8 +574,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,26 +610,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -641,6 +621,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -662,9 +660,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1758"/>
+  <dimension ref="A1:E1759"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23376,8 +23376,19 @@
         <v>240484</v>
       </c>
     </row>
+    <row r="1759" spans="1:3">
+      <c r="A1759" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1759">
+        <v>4973861</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1757">
+  <autoFilter ref="A1:E1758">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1758</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,37 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -242,7 +211,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,16 +232,46 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,15 +285,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,34 +324,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,19 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,97 +380,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,13 +404,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +428,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,15 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,6 +601,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -627,9 +627,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,8 +639,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,10 +662,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1759"/>
+  <dimension ref="A1:E1760"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23387,8 +23387,19 @@
         <v>4973861</v>
       </c>
     </row>
+    <row r="1760" spans="1:3">
+      <c r="A1760" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1760">
+        <v>312175</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1758">
+  <autoFilter ref="A1:E1759">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,6 +210,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -219,7 +227,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,6 +235,52 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,29 +295,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -277,73 +340,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,25 +446,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +494,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,79 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,37 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,16 +571,25 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -597,15 +606,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,11 +627,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,22 +637,22 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -662,8 +660,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1760"/>
+  <dimension ref="A1:E1762"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23398,8 +23398,30 @@
         <v>312175</v>
       </c>
     </row>
+    <row r="1761" spans="1:3">
+      <c r="A1761" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1761">
+        <v>312175</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:3">
+      <c r="A1762" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1762">
+        <v>410453</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1759">
+  <autoFilter ref="A1:E1761">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,18 +203,25 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -225,16 +232,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,14 +264,6 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -266,44 +272,30 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,15 +310,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,14 +319,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +506,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,163 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,17 +580,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,18 +621,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,13 +645,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1762"/>
+  <dimension ref="A1:E1763"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23420,8 +23420,19 @@
         <v>410453</v>
       </c>
     </row>
+    <row r="1763" spans="1:3">
+      <c r="A1763" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1763">
+        <v>4306490</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1761">
+  <autoFilter ref="A1:E1762">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,8 +203,22 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -226,14 +240,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -247,45 +262,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -295,23 +271,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -327,14 +294,47 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +428,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,37 +464,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,49 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,31 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,28 +610,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,6 +634,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -659,160 +668,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1763"/>
+  <dimension ref="A1:E1764"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23431,8 +23431,19 @@
         <v>4306490</v>
       </c>
     </row>
+    <row r="1764" spans="1:3">
+      <c r="A1764" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1764">
+        <v>435738</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1762">
+  <autoFilter ref="A1:E1763">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,43 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -210,8 +247,62 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,59 +317,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,15 +325,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,41 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,19 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +392,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +434,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,13 +494,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,31 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,73 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,30 +572,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -613,8 +589,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,6 +612,17 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
@@ -643,13 +630,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,22 +659,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1764"/>
+  <dimension ref="A1:E1765"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23442,8 +23442,19 @@
         <v>435738</v>
       </c>
     </row>
+    <row r="1765" spans="1:3">
+      <c r="A1765" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1765">
+        <v>273934</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1763">
+  <autoFilter ref="A1:E1764">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,31 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,52 +217,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -301,18 +232,35 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -325,7 +273,67 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,14 +341,6 @@
     <font>
       <b/>
       <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,7 +362,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,49 +488,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,25 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,91 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,58 +589,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +618,214 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1765"/>
+  <dimension ref="A1:E1766"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23453,8 +23453,19 @@
         <v>273934</v>
       </c>
     </row>
+    <row r="1766" spans="1:3">
+      <c r="A1766" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1766">
+        <v>304023</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1764">
+  <autoFilter ref="A1:E1765">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1766</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,14 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,33 +224,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,24 +255,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,22 +294,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,18 +324,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,19 +362,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +434,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +458,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,19 +488,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,37 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,8 +589,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,9 +612,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,18 +639,7 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -668,164 +659,173 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1766"/>
+  <dimension ref="A1:E1767"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23464,8 +23464,19 @@
         <v>304023</v>
       </c>
     </row>
+    <row r="1767" spans="1:3">
+      <c r="A1767" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1767">
+        <v>888522</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1765">
+  <autoFilter ref="A1:E1766">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/Yahoo.xlsx
+++ b/dashboard/data/incoming/Yahoo.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1766</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1767</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,13 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -218,7 +211,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,6 +225,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -240,22 +257,20 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -271,8 +286,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,8 +302,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,47 +333,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,79 +392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +410,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +434,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,13 +464,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,31 +488,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,44 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -586,37 +624,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,35 +654,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,149 +683,149 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1767"/>
+  <dimension ref="A1:E1768"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23475,8 +23475,19 @@
         <v>888522</v>
       </c>
     </row>
+    <row r="1768" spans="1:3">
+      <c r="A1768" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1768">
+        <v>6164007</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1766">
+  <autoFilter ref="A1:E1767">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
